--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260804.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260804.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>17.45%</t>
+          <t>16.85%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.28%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.11%</t>
+          <t>5.14%</t>
         </is>
       </c>
     </row>
@@ -682,95 +682,95 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.40%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,795,000</t>
+          <t>8,060,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>4.27%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>7,600,000</t>
+          <t>1,910,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>4.23%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>41,155,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.70%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>40,000,000</t>
+          <t>1,050,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.55%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
@@ -814,95 +814,95 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>6,400,000</t>
+          <t>1,030,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,030,000</t>
+          <t>7,160,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -924,46 +924,46 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>158,500</t>
+          <t>1,101,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>2,646,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,22 +975,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1007,78 +1007,78 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>3,217,000</t>
+          <t>3,226,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>158,500</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>1,680,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,680,000</t>
+          <t>510,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>897,000</t>
+          <t>1,750,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,750,000</t>
+          <t>897,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1166,73 +1166,73 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>4,400,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,350,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>3,740,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>170,000</t>
+          <t>172,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1452,24 +1452,24 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>650,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,61 +1481,61 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>624,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>624,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>337,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>869,000</t>
+          <t>336,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,39 +1591,39 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>336,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,22 +1635,22 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -1701,39 +1701,35 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>23,694,573,460</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>26,184,060,647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1741,38 +1737,20 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4,793,582,604</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>-3,501,472,226</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
